--- a/data/trans_camb/P43-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P43-Provincia-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16,86</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,56</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,86</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15,66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27,56</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,96; 25,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,02; 23,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,36; 36,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 25,3</t>
+          <t>7,96; 25,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 23,71</t>
+          <t>7,02; 23,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,55; 35,71</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,41; 25,3</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6,85; 23,71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17,55; 35,71</t>
+          <t>18,36; 36,17</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>79,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>48,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>45,03%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>79,23%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,7; 81,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,82; 80,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,77; 118,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,15; 82,94</t>
+          <t>19,7; 81,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,09; 78,43</t>
+          <t>17,82; 80,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,61; 120,32</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,15; 82,94</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17,09; 78,43</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>44,61; 120,32</t>
+          <t>47,77; 118,27</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,64</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,35</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,35</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,36</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14,64</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18,35</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,63; 12,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,28; 21,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,03; 24,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 11,13</t>
+          <t>-0,63; 12,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 20,84</t>
+          <t>9,28; 21,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 24,34</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 11,13</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8,43; 20,84</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12,4; 24,34</t>
+          <t>12,03; 24,55</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40,2%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>50,39%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,45; 36,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,22; 66,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,29; 75,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 33,61</t>
+          <t>-1,45; 36,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,04; 63,42</t>
+          <t>23,22; 66,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,7; 73,92</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-2,29; 33,61</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21,04; 63,42</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31,7; 73,92</t>
+          <t>31,29; 75,78</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,92</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,05</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,98</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15,92</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13,05</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,62; 13,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,65; 23,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,38; 20,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 13,35</t>
+          <t>-1,62; 13,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 23,34</t>
+          <t>8,65; 23,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 20,27</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 13,35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8,7; 23,34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5,57; 20,27</t>
+          <t>5,38; 20,78</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>32,01%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,81; 36,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,9; 64,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,13; 56,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 35,58</t>
+          <t>-3,81; 36,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,17; 63,79</t>
+          <t>19,9; 64,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,63; 55,16</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-4,2; 35,58</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>19,17; 63,79</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>12,63; 55,16</t>
+          <t>12,13; 56,43</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,15</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,98</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>11,61</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5,98</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,25; 15,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,07; 19,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,12; 21,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 14,22</t>
+          <t>0,25; 15,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 18,16</t>
+          <t>4,07; 19,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 21,38</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,01; 14,22</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4,28; 18,16</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-16,77; 21,38</t>
+          <t>-16,12; 21,72</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>14,51%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,46; 40,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,72; 52,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-38,51; 53,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 37,79</t>
+          <t>0,46; 40,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,3; 48,49</t>
+          <t>8,72; 52,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 53,77</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 37,79</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9,3; 48,49</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-37,72; 53,77</t>
+          <t>-38,51; 53,91</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17,84</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22,76</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42,92</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42,92</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>17,84</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>22,76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>42,92</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,48; 26,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,98; 31,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,06; 51,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,81; 26,7</t>
+          <t>8,48; 26,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,06; 31,62</t>
+          <t>12,98; 31,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,62; 50,57</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>7,81; 26,7</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>13,06; 31,62</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>32,62; 50,57</t>
+          <t>35,06; 51,8</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>143,45%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>143,45%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>59,63%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>143,45%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,36; 106,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,39; 130,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>101,5; 225,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,97; 107,75</t>
+          <t>24,36; 106,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>35,85; 126,31</t>
+          <t>37,39; 130,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,58; 201,26</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>23,97; 107,75</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>35,85; 126,31</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>91,58; 201,26</t>
+          <t>101,5; 225,9</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,34</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,68</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,98</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>14,98</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,34</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>11,68</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>14,98</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,36; 18,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,35; 19,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,67; 22,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,38; 18,47</t>
+          <t>1,36; 18,63</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,74; 20,8</t>
+          <t>2,35; 19,69</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,69; 23,0</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,38; 18,47</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3,74; 20,8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6,69; 23,0</t>
+          <t>6,67; 22,48</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>27,02%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>30,52%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>39,15%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,87; 54,38</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,56; 58,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,15; 65,68</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,77; 55,55</t>
+          <t>2,87; 54,38</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,6; 62,54</t>
+          <t>5,56; 58,81</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,47; 67,29</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>3,77; 55,55</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8,6; 62,54</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>15,47; 67,29</t>
+          <t>15,15; 65,68</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,41</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29,96</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>29,96</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>7,41</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>29,96</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,58; 12,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,76; 3,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,67; 45,98</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,18; 13,42</t>
+          <t>1,58; 12,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 3,76</t>
+          <t>-6,76; 3,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,97; 46,24</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2,18; 13,42</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-6,98; 3,76</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>15,97; 46,24</t>
+          <t>16,67; 45,98</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-3,03%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>68,62%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-3,03%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>68,62%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,48; 31,68</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-14,21; 9,39</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,9; 117,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5,04; 33,17</t>
+          <t>3,48; 31,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 8,99</t>
+          <t>-14,21; 9,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,55; 114,38</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>5,04; 33,17</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-14,86; 8,99</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>35,55; 114,38</t>
+          <t>37,9; 117,2</t>
         </is>
       </c>
     </row>
@@ -2136,17 +1688,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16,12</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,33</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2160,21 +1712,6 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>3,33</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>10,23</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>16,12</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>3,33</t>
         </is>
@@ -2189,47 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,42; 15,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,91; 21,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,68; 7,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,19</t>
+          <t>5,42; 15,34</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,16; 21,03</t>
+          <t>10,91; 21,29</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 8,64</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>5,19; 15,19</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>11,16; 21,03</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>-1,18; 8,64</t>
+          <t>-1,68; 7,84</t>
         </is>
       </c>
     </row>
@@ -2242,17 +1764,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2266,21 +1788,6 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>29,77%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>9,7%</t>
         </is>
@@ -2295,47 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,67; 48,34</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,91; 67,38</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,46; 24,55</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14,45; 48,16</t>
+          <t>14,67; 48,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>30,29; 67,67</t>
+          <t>29,91; 67,38</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 26,79</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 48,16</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>30,29; 67,67</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>-3,77; 26,79</t>
+          <t>-4,46; 24,55</t>
         </is>
       </c>
     </row>
@@ -2352,17 +1844,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,02</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,02</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2376,21 +1868,6 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>18,02</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>9,24</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>18,02</t>
         </is>
@@ -2405,47 +1882,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,9; 11,84</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,6; 14,42</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,85; 28,58</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,59</t>
+          <t>6,9; 11,84</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,4; 14,29</t>
+          <t>9,6; 14,42</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,12; 28,66</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>6,75; 11,59</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>9,4; 14,29</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>13,12; 28,66</t>
+          <t>12,85; 28,58</t>
         </is>
       </c>
     </row>
@@ -2458,17 +1920,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2482,21 +1944,6 @@
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>31,72%</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>47,53%</t>
         </is>
@@ -2511,47 +1958,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,47; 32,11</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,39; 39,4</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,93; 75,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17,24; 31,67</t>
+          <t>17,47; 32,11</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>23,98; 39,03</t>
+          <t>24,39; 39,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>34,13; 77,23</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>17,24; 31,67</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>23,98; 39,03</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>34,13; 77,23</t>
+          <t>32,93; 75,01</t>
         </is>
       </c>
     </row>
@@ -2563,7 +1995,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
@@ -2571,7 +2003,6 @@
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P43-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P43-Provincia-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27,56</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,56</t>
+          <t>23,5</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 25,03</t>
+          <t>7,79; 24,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 23,72</t>
+          <t>7,07; 23,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 36,17</t>
+          <t>15,15; 31,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 25,03</t>
+          <t>7,79; 24,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 23,72</t>
+          <t>7,07; 23,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 36,17</t>
+          <t>15,15; 31,69</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,7; 81,61</t>
+          <t>20,06; 81,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 80,2</t>
+          <t>18,65; 79,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,77; 118,27</t>
+          <t>37,17; 106,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,7; 81,61</t>
+          <t>20,06; 81,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 80,2</t>
+          <t>18,65; 79,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,77; 118,27</t>
+          <t>37,17; 106,85</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,35</t>
+          <t>17,18</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,35</t>
+          <t>17,18</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 12,28</t>
+          <t>-1,16; 11,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 21,89</t>
+          <t>8,35; 20,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 24,55</t>
+          <t>11,04; 23,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 12,28</t>
+          <t>-1,16; 11,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 21,89</t>
+          <t>8,35; 20,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 24,55</t>
+          <t>11,04; 23,06</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 36,78</t>
+          <t>-2,98; 35,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,22; 66,46</t>
+          <t>21,59; 62,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,29; 75,78</t>
+          <t>28,42; 69,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 36,78</t>
+          <t>-2,98; 35,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,22; 66,46</t>
+          <t>21,59; 62,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,29; 75,78</t>
+          <t>28,42; 69,25</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>13,03</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 13,6</t>
+          <t>-2,33; 13,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 23,73</t>
+          <t>7,46; 23,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 20,78</t>
+          <t>5,54; 21,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 13,6</t>
+          <t>-2,33; 13,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 23,73</t>
+          <t>7,46; 23,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 20,78</t>
+          <t>5,54; 21,0</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 36,44</t>
+          <t>-5,27; 36,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,9; 64,33</t>
+          <t>15,89; 63,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,13; 56,43</t>
+          <t>12,73; 56,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 36,44</t>
+          <t>-5,27; 36,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,9; 64,33</t>
+          <t>15,89; 63,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,13; 56,43</t>
+          <t>12,73; 56,46</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>10,66</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 15,12</t>
+          <t>-0,37; 14,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 19,8</t>
+          <t>3,88; 19,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 21,72</t>
+          <t>3,68; 18,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 15,12</t>
+          <t>-0,37; 14,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 19,8</t>
+          <t>3,88; 19,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 21,72</t>
+          <t>3,68; 18,68</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 40,44</t>
+          <t>-0,74; 38,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 52,94</t>
+          <t>8,22; 52,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 53,91</t>
+          <t>8,08; 49,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 40,44</t>
+          <t>-0,74; 38,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 52,94</t>
+          <t>8,22; 52,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 53,91</t>
+          <t>8,08; 49,11</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42,92</t>
+          <t>41,36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,92</t>
+          <t>41,36</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,48; 26,95</t>
+          <t>8,36; 26,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12,98; 31,74</t>
+          <t>13,29; 31,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35,06; 51,8</t>
+          <t>31,99; 49,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,48; 26,95</t>
+          <t>8,36; 26,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,98; 31,74</t>
+          <t>13,29; 31,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,06; 51,8</t>
+          <t>31,99; 49,36</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143,45%</t>
+          <t>138,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>143,45%</t>
+          <t>138,25%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24,36; 106,55</t>
+          <t>25,12; 106,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>37,39; 130,94</t>
+          <t>39,09; 126,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101,5; 225,9</t>
+          <t>88,65; 203,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24,36; 106,55</t>
+          <t>25,12; 106,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>37,39; 130,94</t>
+          <t>39,09; 126,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>101,5; 225,9</t>
+          <t>88,65; 203,79</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14,98</t>
+          <t>15,26</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,98</t>
+          <t>15,26</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,36; 18,63</t>
+          <t>1,08; 18,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,35; 19,69</t>
+          <t>2,7; 19,66</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,67; 22,48</t>
+          <t>7,2; 23,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,36; 18,63</t>
+          <t>1,08; 18,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,35; 19,69</t>
+          <t>2,7; 19,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,67; 22,48</t>
+          <t>7,2; 23,1</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,87; 54,38</t>
+          <t>2,86; 52,57</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5,56; 58,81</t>
+          <t>5,95; 57,68</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15,15; 65,68</t>
+          <t>17,15; 67,73</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2,87; 54,38</t>
+          <t>2,86; 52,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,56; 58,81</t>
+          <t>5,95; 57,68</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,15; 65,68</t>
+          <t>17,15; 67,73</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29,96</t>
+          <t>17,45</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,96</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,58; 12,81</t>
+          <t>1,75; 12,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 3,82</t>
+          <t>-7,04; 4,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16,67; 45,98</t>
+          <t>11,66; 22,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,58; 12,81</t>
+          <t>1,75; 12,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 3,82</t>
+          <t>-7,04; 4,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,67; 45,98</t>
+          <t>11,66; 22,74</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,48; 31,68</t>
+          <t>3,47; 30,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 9,39</t>
+          <t>-15,41; 10,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>37,9; 117,2</t>
+          <t>25,15; 56,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,48; 31,68</t>
+          <t>3,47; 30,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 9,39</t>
+          <t>-15,41; 10,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,9; 117,2</t>
+          <t>25,15; 56,77</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>2,79</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,34</t>
+          <t>5,26; 15,74</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10,91; 21,29</t>
+          <t>11,26; 20,87</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 7,84</t>
+          <t>-1,64; 7,72</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,34</t>
+          <t>5,26; 15,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10,91; 21,29</t>
+          <t>11,26; 20,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 7,84</t>
+          <t>-1,64; 7,72</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1802,32 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,67; 48,34</t>
+          <t>14,21; 49,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>29,91; 67,38</t>
+          <t>30,77; 67,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 24,55</t>
+          <t>-4,34; 24,76</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14,67; 48,34</t>
+          <t>14,21; 49,62</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>29,91; 67,38</t>
+          <t>30,77; 67,46</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 24,55</t>
+          <t>-4,34; 24,76</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>18,02</t>
+          <t>14,42</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,02</t>
+          <t>14,42</t>
         </is>
       </c>
     </row>
@@ -1882,32 +1882,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,84</t>
+          <t>6,91; 11,76</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,42</t>
+          <t>9,69; 14,52</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12,85; 28,58</t>
+          <t>12,16; 16,83</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,84</t>
+          <t>6,91; 11,76</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,42</t>
+          <t>9,69; 14,52</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,85; 28,58</t>
+          <t>12,16; 16,83</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -1958,32 +1958,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17,47; 32,11</t>
+          <t>17,55; 31,96</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>24,39; 39,4</t>
+          <t>24,93; 39,65</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>32,93; 75,01</t>
+          <t>30,88; 45,91</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17,47; 32,11</t>
+          <t>17,55; 31,96</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>24,39; 39,4</t>
+          <t>24,93; 39,65</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>32,93; 75,01</t>
+          <t>30,88; 45,91</t>
         </is>
       </c>
     </row>
